--- a/results/Resultados Obtidos.xlsx
+++ b/results/Resultados Obtidos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Faculdade\POS-GRADUACAO\Modelos Multimodais\atelie-generativo-estilo-pixel-art\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roderiok\OneDrive\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838EFE83-7590-482D-8114-94F2B4967150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8470C178-31A0-45A0-AC48-7E2242078210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC655C6F-F153-4B59-B0EE-1DE4965B63D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{AC655C6F-F153-4B59-B0EE-1DE4965B63D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="6">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -79,8 +79,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="6">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -95,13 +102,16 @@
     </bk>
     <bk>
       <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t xml:space="preserve"> num_inference_steps=100,
     guidance_scale=9.0
@@ -158,6 +168,24 @@
   </si>
   <si>
     <t>parametros prompt</t>
+  </si>
+  <si>
+    <t>rank=32
+max_train_steps=1200</t>
+  </si>
+  <si>
+    <t>"estilo_pixel_art, cena em pixel art com uma fazenda, pomar de frutas e um lago azul."</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> num_inference_steps=180,
+    guidance_scale=9.0
+</t>
+  </si>
+  <si>
+    <t>Google Colab</t>
+  </si>
+  <si>
+    <t>Rodério Kunz</t>
   </si>
 </sst>
 </file>
@@ -270,7 +298,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -289,6 +317,10 @@
   </rv>
   <rv s="0">
     <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -310,6 +342,7 @@
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
 </richValueRels>
 </file>
 
@@ -761,12 +794,24 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
